--- a/cumpleanos.xlsx
+++ b/cumpleanos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://controlesempresarialesltda-my.sharepoint.com/personal/marango_coem_co/Documents/GitHub/COEM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="206" documentId="8_{058768CC-3012-4FE7-96DF-03842296FC79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E48D5DE9-7FFA-4A0D-B439-9C43847623DD}"/>
+  <xr:revisionPtr revIDLastSave="209" documentId="8_{058768CC-3012-4FE7-96DF-03842296FC79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6A24F02-B476-4F62-B178-5C59A0F17190}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FFD0B6FF-8ACF-4643-8209-7E393FF170EB}"/>
   </bookViews>
@@ -36,10 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="44">
-  <si>
-    <t>DIA</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="45">
   <si>
     <t>MES</t>
   </si>
@@ -50,9 +47,6 @@
     <t>FERNANDO C</t>
   </si>
   <si>
-    <t>22</t>
-  </si>
-  <si>
     <t>ENERO</t>
   </si>
   <si>
@@ -168,6 +162,15 @@
   </si>
   <si>
     <t>NOMBRE</t>
+  </si>
+  <si>
+    <t>CUMPLEAÑOS</t>
+  </si>
+  <si>
+    <t>22 ENERO</t>
+  </si>
+  <si>
+    <t>16 MARZO</t>
   </si>
 </sst>
 </file>
@@ -595,213 +598,213 @@
   <sheetData>
     <row r="1" spans="1:7" ht="25.8" x14ac:dyDescent="0.5">
       <c r="A1" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="25.8" x14ac:dyDescent="0.5">
       <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="D2" s="3" t="s">
         <v>4</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>7</v>
-      </c>
-      <c r="B3" s="5">
-        <v>16</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A4" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A5" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B5" s="5">
         <v>31</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="D6" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A7" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A8" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B8" s="5">
         <v>21</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="D9" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>26</v>
       </c>
       <c r="G9" s="7"/>
     </row>
     <row r="10" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A10" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="D11" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="D12" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="D13" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A14" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B14" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A15" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/cumpleanos.xlsx
+++ b/cumpleanos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://controlesempresarialesltda-my.sharepoint.com/personal/marango_coem_co/Documents/GitHub/COEM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="209" documentId="8_{058768CC-3012-4FE7-96DF-03842296FC79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6A24F02-B476-4F62-B178-5C59A0F17190}"/>
+  <xr:revisionPtr revIDLastSave="246" documentId="8_{058768CC-3012-4FE7-96DF-03842296FC79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE58C55A-8E24-4F8A-8677-0C555DCF3AF1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FFD0B6FF-8ACF-4643-8209-7E393FF170EB}"/>
   </bookViews>
@@ -36,10 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="45">
-  <si>
-    <t>MES</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="25">
   <si>
     <t>SIGNO</t>
   </si>
@@ -47,111 +44,60 @@
     <t>FERNANDO C</t>
   </si>
   <si>
-    <t>ENERO</t>
-  </si>
-  <si>
     <t>ACUARIO</t>
   </si>
   <si>
     <t>OMAR</t>
   </si>
   <si>
-    <t>MARZO</t>
-  </si>
-  <si>
     <t>PISCIS</t>
   </si>
   <si>
     <t>JENNIFER</t>
   </si>
   <si>
-    <t>19</t>
-  </si>
-  <si>
     <t>HAROLD</t>
   </si>
   <si>
-    <t>MAYO</t>
-  </si>
-  <si>
     <t>GEMINIS</t>
   </si>
   <si>
     <t>JAIME</t>
   </si>
   <si>
-    <t>01</t>
-  </si>
-  <si>
-    <t>JUNIO</t>
-  </si>
-  <si>
     <t>WILLIAM</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>LORENA</t>
   </si>
   <si>
-    <t>JULIO</t>
-  </si>
-  <si>
     <t>CANCER</t>
   </si>
   <si>
     <t>FERNANDO S</t>
   </si>
   <si>
-    <t>08</t>
-  </si>
-  <si>
-    <t>AGOSTO</t>
-  </si>
-  <si>
     <t>LEO</t>
   </si>
   <si>
     <t>SANTIAGO</t>
   </si>
   <si>
-    <t>17</t>
-  </si>
-  <si>
     <t>JOSE</t>
   </si>
   <si>
-    <t>06</t>
-  </si>
-  <si>
-    <t>SEPTIEMBRE</t>
-  </si>
-  <si>
     <t>VIRGO</t>
   </si>
   <si>
     <t>SANDRA</t>
   </si>
   <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>OCTUBRE</t>
-  </si>
-  <si>
     <t>ESCORPION</t>
   </si>
   <si>
     <t>ROMMY</t>
   </si>
   <si>
-    <t>05</t>
-  </si>
-  <si>
-    <t>DICIEMBRE</t>
-  </si>
-  <si>
     <t>SAGITARIO</t>
   </si>
   <si>
@@ -165,12 +111,6 @@
   </si>
   <si>
     <t>CUMPLEAÑOS</t>
-  </si>
-  <si>
-    <t>22 ENERO</t>
-  </si>
-  <si>
-    <t>16 MARZO</t>
   </si>
 </sst>
 </file>
@@ -236,7 +176,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -248,11 +188,10 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -587,224 +526,178 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11ACE27C-718F-45BF-82B9-A30F519490E3}">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.88671875" customWidth="1"/>
-    <col min="2" max="2" width="10" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.8" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:6" ht="25.8" x14ac:dyDescent="0.5">
       <c r="A1" s="2" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:6" ht="25.8" x14ac:dyDescent="0.5">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="6">
+        <v>46044</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="3" t="s">
+    </row>
+    <row r="3" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="B3" s="6">
+        <v>46097</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A3" s="2" t="s">
+    <row r="4" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C3" s="3" t="s">
+      <c r="B4" s="6">
+        <v>46100</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="B5" s="6">
+        <v>46173</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="2" t="s">
+    <row r="6" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B6" s="6">
+        <v>46174</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="B7" s="6">
+        <v>46178</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A5" s="2" t="s">
+    <row r="8" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="5">
-        <v>31</v>
-      </c>
-      <c r="C5" s="3" t="s">
+      <c r="B8" s="6">
+        <v>46224</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="3" t="s">
+    </row>
+    <row r="9" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="2" t="s">
+      <c r="B9" s="6">
+        <v>46242</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="F9" s="5"/>
+    </row>
+    <row r="10" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="B10" s="6">
+        <v>46251</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A7" s="2" t="s">
+      <c r="B11" s="6">
+        <v>46271</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="5" t="s">
+    </row>
+    <row r="12" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="2" t="s">
+      <c r="B12" s="6">
+        <v>46326</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="5">
+    </row>
+    <row r="13" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="6">
+        <v>46361</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="3" t="s">
+      <c r="B14" s="6">
+        <v>46361</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A9" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="5" t="s">
+    <row r="15" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9" s="7"/>
-    </row>
-    <row r="10" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A11" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A12" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A13" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A14" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A15" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>26</v>
+      <c r="B15" s="6">
+        <v>46373</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/cumpleanos.xlsx
+++ b/cumpleanos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://controlesempresarialesltda-my.sharepoint.com/personal/marango_coem_co/Documents/GitHub/COEM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="246" documentId="8_{058768CC-3012-4FE7-96DF-03842296FC79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE58C55A-8E24-4F8A-8677-0C555DCF3AF1}"/>
+  <xr:revisionPtr revIDLastSave="249" documentId="8_{058768CC-3012-4FE7-96DF-03842296FC79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92635FB3-4BE7-4F90-AEC7-484493057B64}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FFD0B6FF-8ACF-4643-8209-7E393FF170EB}"/>
+    <workbookView minimized="1" xWindow="1836" yWindow="1836" windowWidth="17256" windowHeight="8856" xr2:uid="{FFD0B6FF-8ACF-4643-8209-7E393FF170EB}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -107,10 +107,10 @@
     <t>RUBEN</t>
   </si>
   <si>
-    <t>NOMBRE</t>
-  </si>
-  <si>
-    <t>CUMPLEAÑOS</t>
+    <t>Nombre</t>
+  </si>
+  <si>
+    <t>Cumpleaños</t>
   </si>
 </sst>
 </file>
@@ -189,7 +189,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="16" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>

--- a/cumpleanos.xlsx
+++ b/cumpleanos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://controlesempresarialesltda-my.sharepoint.com/personal/marango_coem_co/Documents/GitHub/COEM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="249" documentId="8_{058768CC-3012-4FE7-96DF-03842296FC79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92635FB3-4BE7-4F90-AEC7-484493057B64}"/>
+  <xr:revisionPtr revIDLastSave="253" documentId="8_{058768CC-3012-4FE7-96DF-03842296FC79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0DEB808-C5FE-4797-A27F-0058A7171A43}"/>
   <bookViews>
     <workbookView minimized="1" xWindow="1836" yWindow="1836" windowWidth="17256" windowHeight="8856" xr2:uid="{FFD0B6FF-8ACF-4643-8209-7E393FF170EB}"/>
   </bookViews>
@@ -41,9 +41,6 @@
     <t>SIGNO</t>
   </si>
   <si>
-    <t>FERNANDO C</t>
-  </si>
-  <si>
     <t>ACUARIO</t>
   </si>
   <si>
@@ -74,9 +71,6 @@
     <t>CANCER</t>
   </si>
   <si>
-    <t>FERNANDO S</t>
-  </si>
-  <si>
     <t>LEO</t>
   </si>
   <si>
@@ -111,6 +105,12 @@
   </si>
   <si>
     <t>Cumpleaños</t>
+  </si>
+  <si>
+    <t>SOTO FERNANDO</t>
+  </si>
+  <si>
+    <t>CORELLA FERNANDO</t>
   </si>
 </sst>
 </file>
@@ -529,17 +529,17 @@
   <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.88671875" customWidth="1"/>
+    <col min="1" max="1" width="33.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="25.8" x14ac:dyDescent="0.5">
       <c r="A1" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -547,157 +547,157 @@
     </row>
     <row r="2" spans="1:6" ht="25.8" x14ac:dyDescent="0.5">
       <c r="A2" s="2" t="s">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="B2" s="6">
         <v>46044</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A3" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" s="6">
         <v>46097</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A4" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4" s="6">
         <v>46100</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A5" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" s="6">
         <v>46173</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A6" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" s="6">
         <v>46174</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" s="6">
         <v>46178</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A8" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8" s="6">
         <v>46224</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A9" s="2" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="B9" s="6">
         <v>46242</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F9" s="5"/>
     </row>
     <row r="10" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A10" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B10" s="6">
         <v>46251</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A11" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B11" s="6">
         <v>46271</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A12" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B12" s="6">
         <v>46326</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A13" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B13" s="6">
         <v>46361</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A14" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B14" s="6">
         <v>46361</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A15" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B15" s="6">
         <v>46373</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
